--- a/docs/analysis/PSD-curve-fitting.xlsx
+++ b/docs/analysis/PSD-curve-fitting.xlsx
@@ -1,19 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23530"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\moran\OneDrive\바탕 화면\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{778EB0DE-8E64-499C-A277-4D40B4BD5D23}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="3036" yWindow="3036" windowWidth="16584" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="시트2" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="시트1" sheetId="2" r:id="rId5"/>
-    <sheet state="visible" name="시트1의 사본" sheetId="3" r:id="rId6"/>
+    <sheet name="시트2" sheetId="1" r:id="rId1"/>
+    <sheet name="시트1" sheetId="2" r:id="rId2"/>
+    <sheet name="시트1의 사본" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="63">
   <si>
     <t>d1=51.83*exp( -0.001981*x)+17.8*exp( -0.0004166*x)</t>
   </si>
@@ -27,9 +47,6 @@
     <t>d4 =  57.7*exp( -0.002206 *x)+  19.1*exp(  -0.0004304*x)</t>
   </si>
   <si>
-    <t>d5 = 490.1 *exp( -0.004111*x)+  24.61*exp(  -0.0004845*x)</t>
-  </si>
-  <si>
     <t>d6 =  638.6 *exp( -0.004488 *x)+    26.45 *exp( -0.000508*x)</t>
   </si>
   <si>
@@ -114,72 +131,48 @@
     <t>a =        57.7  (55.13, 60.27)</t>
   </si>
   <si>
-    <t>a =       490.1  (370.4, 609.8)</t>
-  </si>
-  <si>
     <t>a =       638.6  (292.3, 984.9)</t>
   </si>
   <si>
     <t>b =   -0.002206  (-0.002395, -0.002017)</t>
   </si>
   <si>
-    <t>b =   -0.004111  (-0.004438, -0.003784)</t>
-  </si>
-  <si>
     <t>b =   -0.004488  (-0.005192, -0.003784)</t>
   </si>
   <si>
     <t>c =        19.1  (16.8, 21.41)</t>
   </si>
   <si>
-    <t>c =       24.61  (22.79, 26.44)</t>
-  </si>
-  <si>
     <t>c =       26.45  (23.16, 29.75)</t>
   </si>
   <si>
     <t>d =  -0.0004304  (-0.0004726, -0.0003882)</t>
   </si>
   <si>
-    <t>d =  -0.0004845  (-0.0005163, -0.0004527)</t>
-  </si>
-  <si>
     <t>d =   -0.000508  (-0.0005637, -0.0004524)</t>
   </si>
   <si>
     <t>SSE: 1.147</t>
   </si>
   <si>
-    <t>SSE: 2.086</t>
-  </si>
-  <si>
     <t>SSE: 7.398</t>
   </si>
   <si>
     <t>결정계수: 0.9996</t>
   </si>
   <si>
-    <t>결정계수: 0.9992</t>
-  </si>
-  <si>
     <t>결정계수: 0.9973</t>
   </si>
   <si>
     <t>수정된 결정계수: 0.9995</t>
   </si>
   <si>
-    <t>수정된 결정계수: 0.9992</t>
-  </si>
-  <si>
     <t>수정된 결정계수: 0.9971</t>
   </si>
   <si>
     <t>RMSE: 0.1738</t>
   </si>
   <si>
-    <t>RMSE: 0.2343</t>
-  </si>
-  <si>
     <t>RMSE: 0.4412</t>
   </si>
   <si>
@@ -190,24 +183,230 @@
   </si>
   <si>
     <t>try</t>
+  </si>
+  <si>
+    <r>
+      <t>일반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>모델</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> Exp2:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">     f(x) = a*exp(b*x) + c*exp(d*x)</t>
+  </si>
+  <si>
+    <r>
+      <t>계수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>신뢰한계</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>: 95%):</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>피팅의</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>적합도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">  SSE: 2.769</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결정계수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>: 0.999</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>수정된</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="돋움"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>결정계수</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+      </rPr>
+      <t>: 0.9989</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">  RMSE: 0.2699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       a =       904.3  (645.6, 1163)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>d5 = 904.3 *exp( -0.004111*x)+  24.61*exp(  -0.0004845*x)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">       b =   -0.004669  (-0.005032, -0.004307)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">       c =       23.23  (21.43, 25.03)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">       d =  -0.0004703  (-0.0005051, -0.0004356)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -215,7 +414,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -225,33 +424,44 @@
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
@@ -262,11 +472,17 @@
     <xdr:ext cx="10372725" cy="8467725"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="0" name="image1.png" title="이미지"/>
+        <xdr:cNvPr id="2" name="image1.png" title="이미지">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr preferRelativeResize="0"/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -283,16 +499,8 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -482,354 +690,361 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A2:G45"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>1</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="G15" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="D15" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="G15" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
+      <c r="D16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G17" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G18" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
+      <c r="D19" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="1" t="s">
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="G20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
+      <c r="D21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="G21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G21" s="1" t="s">
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="s">
+      <c r="D22" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="G22" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="1" t="s">
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="s">
+      <c r="D24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="G25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G25" s="1" t="s">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="G26" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G26" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="s">
+      <c r="D27" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="G27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="G27" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="G28" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="G28" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30">
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="32">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D32" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G32" s="1">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D34" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G33" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="s">
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D35" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G34" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="36">
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D36" s="1" t="s">
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="D37" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="s">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D38" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G37" s="1" t="s">
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="s">
+      <c r="D39" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G39" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D38" s="1" t="s">
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="D42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="s">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D43" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G39" s="1" t="s">
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="s">
+      <c r="D44" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="G44" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D42" s="1" t="s">
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="D45" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="G45" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G45" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="3" max="22" width="8.14"/>
+    <col min="3" max="22" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -845,1328 +1060,1330 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G2" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L2" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="M2" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="N2" s="2">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="O2" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="P2" s="2">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>3608.0</v>
+        <v>3608</v>
       </c>
       <c r="D3" s="1">
-        <v>2706.0</v>
+        <v>2706</v>
       </c>
       <c r="E3" s="1">
-        <v>2149.0</v>
+        <v>2149</v>
       </c>
       <c r="F3" s="1">
-        <v>1780.0</v>
+        <v>1780</v>
       </c>
       <c r="G3" s="1">
-        <v>1526.0</v>
+        <v>1526</v>
       </c>
       <c r="H3" s="1">
-        <v>1335.0</v>
+        <v>1335</v>
       </c>
       <c r="I3" s="1">
-        <v>1167.0</v>
+        <v>1167</v>
       </c>
       <c r="J3" s="1">
-        <v>1040.0</v>
+        <v>1040</v>
       </c>
       <c r="K3" s="1">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="L3" s="1">
-        <v>848.0</v>
+        <v>848</v>
       </c>
       <c r="M3" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="N3" s="1">
-        <v>711.0</v>
+        <v>711</v>
       </c>
       <c r="O3" s="1">
-        <v>647.0</v>
+        <v>647</v>
       </c>
       <c r="P3" s="1">
-        <v>582.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>3608.0</v>
+        <v>3608</v>
       </c>
       <c r="D4" s="1">
-        <v>2706.0</v>
+        <v>2706</v>
       </c>
       <c r="E4" s="1">
-        <v>2147.0</v>
+        <v>2147</v>
       </c>
       <c r="F4" s="1">
-        <v>1781.0</v>
+        <v>1781</v>
       </c>
       <c r="G4" s="1">
-        <v>1526.0</v>
+        <v>1526</v>
       </c>
       <c r="H4" s="1">
-        <v>1336.0</v>
+        <v>1336</v>
       </c>
       <c r="I4" s="1">
-        <v>1167.0</v>
+        <v>1167</v>
       </c>
       <c r="J4" s="1">
-        <v>1040.0</v>
+        <v>1040</v>
       </c>
       <c r="K4" s="1">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="L4" s="1">
-        <v>848.0</v>
+        <v>848</v>
       </c>
       <c r="M4" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="N4" s="1">
-        <v>711.0</v>
+        <v>711</v>
       </c>
       <c r="O4" s="1">
-        <v>647.0</v>
+        <v>647</v>
       </c>
       <c r="P4" s="1">
-        <v>582.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>3609.0</v>
+        <v>3609</v>
       </c>
       <c r="D5" s="1">
-        <v>2705.0</v>
+        <v>2705</v>
       </c>
       <c r="E5" s="1">
-        <v>2141.0</v>
+        <v>2141</v>
       </c>
       <c r="F5" s="1">
-        <v>1780.0</v>
+        <v>1780</v>
       </c>
       <c r="G5" s="1">
-        <v>1526.0</v>
+        <v>1526</v>
       </c>
       <c r="H5" s="1">
-        <v>1335.0</v>
+        <v>1335</v>
       </c>
       <c r="I5" s="1">
-        <v>1167.0</v>
+        <v>1167</v>
       </c>
       <c r="J5" s="1">
-        <v>1040.0</v>
+        <v>1040</v>
       </c>
       <c r="K5" s="1">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="L5" s="1">
-        <v>847.0</v>
+        <v>847</v>
       </c>
       <c r="M5" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="N5" s="1">
-        <v>711.0</v>
+        <v>711</v>
       </c>
       <c r="O5" s="1">
-        <v>646.0</v>
+        <v>646</v>
       </c>
       <c r="P5" s="1">
-        <v>603.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C6" s="3">
-        <f t="shared" ref="C6:P6" si="1">STDEV(C3:C5)</f>
-        <v>0.5773502692</v>
+        <f t="shared" ref="C6:P6" si="0">STDEV(C3:C5)</f>
+        <v>0.57735026918962584</v>
       </c>
       <c r="D6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="E6" s="3">
-        <f t="shared" si="1"/>
-        <v>4.163331999</v>
+        <f t="shared" si="0"/>
+        <v>4.1633319989322661</v>
       </c>
       <c r="F6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="G6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="I6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962573</v>
       </c>
       <c r="M6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N6" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="O6" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962573</v>
       </c>
       <c r="P6" s="3">
-        <f t="shared" si="1"/>
-        <v>12.12435565</v>
+        <f t="shared" si="0"/>
+        <v>12.124355652982141</v>
       </c>
       <c r="Q6" s="3">
         <f>AVERAGE(C6:P6)</f>
-        <v>1.410842091</v>
+        <v>1.4108420905037258</v>
       </c>
       <c r="R6" s="1">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>3901.0</v>
+        <v>3901</v>
       </c>
       <c r="D7" s="1">
-        <v>2876.0</v>
+        <v>2876</v>
       </c>
       <c r="E7" s="1">
-        <v>2257.0</v>
+        <v>2257</v>
       </c>
       <c r="F7" s="1">
-        <v>1883.0</v>
+        <v>1883</v>
       </c>
       <c r="G7" s="1">
-        <v>1604.0</v>
+        <v>1604</v>
       </c>
       <c r="H7" s="1">
-        <v>1378.0</v>
+        <v>1378</v>
       </c>
       <c r="I7" s="1">
-        <v>1218.0</v>
+        <v>1218</v>
       </c>
       <c r="J7" s="1">
-        <v>1091.0</v>
+        <v>1091</v>
       </c>
       <c r="K7" s="1">
-        <v>965.0</v>
+        <v>965</v>
       </c>
       <c r="L7" s="1">
-        <v>906.0</v>
+        <v>906</v>
       </c>
       <c r="M7" s="1">
-        <v>793.0</v>
+        <v>793</v>
       </c>
       <c r="N7" s="1">
-        <v>731.0</v>
+        <v>731</v>
       </c>
       <c r="O7" s="1">
-        <v>663.0</v>
+        <v>663</v>
       </c>
       <c r="P7" s="1">
-        <v>611.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>3900.0</v>
+        <v>3900</v>
       </c>
       <c r="D8" s="1">
-        <v>2877.0</v>
+        <v>2877</v>
       </c>
       <c r="E8" s="1">
-        <v>2260.0</v>
+        <v>2260</v>
       </c>
       <c r="F8" s="1">
-        <v>1881.0</v>
+        <v>1881</v>
       </c>
       <c r="G8" s="1">
-        <v>1602.0</v>
+        <v>1602</v>
       </c>
       <c r="H8" s="1">
-        <v>1379.0</v>
+        <v>1379</v>
       </c>
       <c r="I8" s="1">
-        <v>1216.0</v>
+        <v>1216</v>
       </c>
       <c r="J8" s="1">
-        <v>1095.0</v>
+        <v>1095</v>
       </c>
       <c r="K8" s="1">
-        <v>964.0</v>
+        <v>964</v>
       </c>
       <c r="L8" s="1">
-        <v>889.0</v>
+        <v>889</v>
       </c>
       <c r="M8" s="1">
-        <v>794.0</v>
+        <v>794</v>
       </c>
       <c r="N8" s="1">
-        <v>728.0</v>
+        <v>728</v>
       </c>
       <c r="O8" s="1">
-        <v>665.0</v>
+        <v>665</v>
       </c>
       <c r="P8" s="1">
-        <v>604.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>3901.0</v>
+        <v>3901</v>
       </c>
       <c r="D9" s="1">
-        <v>2880.0</v>
+        <v>2880</v>
       </c>
       <c r="E9" s="1">
-        <v>2260.0</v>
+        <v>2260</v>
       </c>
       <c r="F9" s="1">
-        <v>1881.0</v>
+        <v>1881</v>
       </c>
       <c r="G9" s="1">
-        <v>1603.0</v>
+        <v>1603</v>
       </c>
       <c r="H9" s="1">
-        <v>1378.0</v>
+        <v>1378</v>
       </c>
       <c r="I9" s="1">
-        <v>1219.0</v>
+        <v>1219</v>
       </c>
       <c r="J9" s="1">
-        <v>1095.0</v>
+        <v>1095</v>
       </c>
       <c r="K9" s="1">
-        <v>967.0</v>
+        <v>967</v>
       </c>
       <c r="L9" s="1">
-        <v>905.0</v>
+        <v>905</v>
       </c>
       <c r="M9" s="1">
-        <v>794.0</v>
+        <v>794</v>
       </c>
       <c r="N9" s="1">
-        <v>732.0</v>
+        <v>732</v>
       </c>
       <c r="O9" s="1">
-        <v>668.0</v>
+        <v>668</v>
       </c>
       <c r="P9" s="1">
-        <v>629.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C10" s="3">
-        <f t="shared" ref="C10:P10" si="2">STDEV(C7:C9)</f>
-        <v>0.5773502692</v>
+        <f t="shared" ref="C10:P10" si="1">STDEV(C7:C9)</f>
+        <v>0.57735026918962584</v>
       </c>
       <c r="D10" s="3">
-        <f t="shared" si="2"/>
-        <v>2.081665999</v>
+        <f t="shared" si="1"/>
+        <v>2.0816659994661326</v>
       </c>
       <c r="E10" s="3">
-        <f t="shared" si="2"/>
-        <v>1.732050808</v>
+        <f t="shared" si="1"/>
+        <v>1.7320508075688772</v>
       </c>
       <c r="F10" s="3">
-        <f t="shared" si="2"/>
-        <v>1.154700538</v>
+        <f t="shared" si="1"/>
+        <v>1.1547005383792515</v>
       </c>
       <c r="G10" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="H10" s="3">
-        <f t="shared" si="2"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="1"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="I10" s="3">
-        <f t="shared" si="2"/>
-        <v>1.527525232</v>
+        <f t="shared" si="1"/>
+        <v>1.5275252316519465</v>
       </c>
       <c r="J10" s="3">
-        <f t="shared" si="2"/>
-        <v>2.309401077</v>
+        <f t="shared" si="1"/>
+        <v>2.3094010767585034</v>
       </c>
       <c r="K10" s="3">
-        <f t="shared" si="2"/>
-        <v>1.527525232</v>
+        <f t="shared" si="1"/>
+        <v>1.5275252316519468</v>
       </c>
       <c r="L10" s="3">
-        <f t="shared" si="2"/>
-        <v>9.539392014</v>
+        <f t="shared" si="1"/>
+        <v>9.5393920141694561</v>
       </c>
       <c r="M10" s="3">
-        <f t="shared" si="2"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="1"/>
+        <v>0.57735026918962573</v>
       </c>
       <c r="N10" s="3">
-        <f t="shared" si="2"/>
-        <v>2.081665999</v>
+        <f t="shared" si="1"/>
+        <v>2.0816659994661331</v>
       </c>
       <c r="O10" s="3">
-        <f t="shared" si="2"/>
-        <v>2.516611478</v>
+        <f t="shared" si="1"/>
+        <v>2.5166114784235836</v>
       </c>
       <c r="P10" s="3">
-        <f t="shared" si="2"/>
-        <v>12.89702808</v>
+        <f t="shared" si="1"/>
+        <v>12.897028081435403</v>
       </c>
       <c r="Q10" s="3">
         <f>AVERAGE(C10:P10)</f>
-        <v>2.864258376</v>
+        <v>2.8642583761814366</v>
       </c>
       <c r="R10" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>4085.0</v>
+        <v>4085</v>
       </c>
       <c r="D11" s="1">
-        <v>3012.0</v>
+        <v>3012</v>
       </c>
       <c r="E11" s="1">
-        <v>2340.0</v>
+        <v>2340</v>
       </c>
       <c r="F11" s="1">
-        <v>1907.0</v>
+        <v>1907</v>
       </c>
       <c r="G11" s="1">
-        <v>1641.0</v>
+        <v>1641</v>
       </c>
       <c r="H11" s="1">
-        <v>1420.0</v>
+        <v>1420</v>
       </c>
       <c r="I11" s="1">
-        <v>1229.0</v>
+        <v>1229</v>
       </c>
       <c r="J11" s="1">
-        <v>1091.0</v>
+        <v>1091</v>
       </c>
       <c r="K11" s="1">
-        <v>991.0</v>
+        <v>991</v>
       </c>
       <c r="L11" s="1">
-        <v>896.0</v>
+        <v>896</v>
       </c>
       <c r="M11" s="1">
-        <v>803.0</v>
+        <v>803</v>
       </c>
       <c r="N11" s="1">
-        <v>739.0</v>
+        <v>739</v>
       </c>
       <c r="O11" s="1">
-        <v>675.0</v>
+        <v>675</v>
       </c>
       <c r="P11" s="1">
-        <v>608.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1">
-        <v>4085.0</v>
+        <v>4085</v>
       </c>
       <c r="D12" s="1">
-        <v>3012.0</v>
+        <v>3012</v>
       </c>
       <c r="E12" s="1">
-        <v>2341.0</v>
+        <v>2341</v>
       </c>
       <c r="F12" s="1">
-        <v>1907.0</v>
+        <v>1907</v>
       </c>
       <c r="G12" s="1">
-        <v>1641.0</v>
+        <v>1641</v>
       </c>
       <c r="H12" s="1">
-        <v>1421.0</v>
+        <v>1421</v>
       </c>
       <c r="I12" s="1">
-        <v>1229.0</v>
+        <v>1229</v>
       </c>
       <c r="J12" s="1">
-        <v>1091.0</v>
+        <v>1091</v>
       </c>
       <c r="K12" s="1">
-        <v>991.0</v>
+        <v>991</v>
       </c>
       <c r="L12" s="1">
-        <v>896.0</v>
+        <v>896</v>
       </c>
       <c r="M12" s="1">
-        <v>803.0</v>
+        <v>803</v>
       </c>
       <c r="N12" s="1">
-        <v>739.0</v>
+        <v>739</v>
       </c>
       <c r="O12" s="1">
-        <v>675.0</v>
+        <v>675</v>
       </c>
       <c r="P12" s="1">
-        <v>608.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>4086.0</v>
+        <v>4086</v>
       </c>
       <c r="D13" s="1">
-        <v>3012.0</v>
+        <v>3012</v>
       </c>
       <c r="E13" s="1">
-        <v>2340.0</v>
+        <v>2340</v>
       </c>
       <c r="F13" s="1">
-        <v>1907.0</v>
+        <v>1907</v>
       </c>
       <c r="G13" s="1">
-        <v>1641.0</v>
+        <v>1641</v>
       </c>
       <c r="H13" s="1">
-        <v>1420.0</v>
+        <v>1420</v>
       </c>
       <c r="I13" s="1">
-        <v>1229.0</v>
+        <v>1229</v>
       </c>
       <c r="J13" s="1">
-        <v>1091.0</v>
+        <v>1091</v>
       </c>
       <c r="K13" s="1">
-        <v>991.0</v>
+        <v>991</v>
       </c>
       <c r="L13" s="1">
-        <v>870.0</v>
+        <v>870</v>
       </c>
       <c r="M13" s="1">
-        <v>803.0</v>
+        <v>803</v>
       </c>
       <c r="N13" s="1">
-        <v>739.0</v>
+        <v>739</v>
       </c>
       <c r="O13" s="1">
-        <v>675.0</v>
+        <v>675</v>
       </c>
       <c r="P13" s="1">
-        <v>608.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C14" s="3">
-        <f t="shared" ref="C14:P14" si="3">STDEV(C11:C13)</f>
-        <v>0.5773502692</v>
+        <f t="shared" ref="C14:P14" si="2">STDEV(C11:C13)</f>
+        <v>0.57735026918962584</v>
       </c>
       <c r="D14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E14" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="2"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="F14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H14" s="3">
-        <f t="shared" si="3"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="2"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="I14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="J14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="K14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="L14" s="3">
-        <f t="shared" si="3"/>
-        <v>15.011107</v>
+        <f t="shared" si="2"/>
+        <v>15.01110699893027</v>
       </c>
       <c r="M14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="N14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="O14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P14" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="Q14" s="3">
         <f>AVERAGE(C14:P14)</f>
-        <v>1.195939843</v>
+        <v>1.1959398433213677</v>
       </c>
       <c r="R14" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>3659.0</v>
+        <v>3659</v>
       </c>
       <c r="D15" s="1">
-        <v>2755.0</v>
+        <v>2755</v>
       </c>
       <c r="E15" s="1">
-        <v>2156.0</v>
+        <v>2156</v>
       </c>
       <c r="F15" s="1">
-        <v>1758.0</v>
+        <v>1758</v>
       </c>
       <c r="G15" s="1">
-        <v>1525.0</v>
+        <v>1525</v>
       </c>
       <c r="H15" s="1">
-        <v>1326.0</v>
+        <v>1326</v>
       </c>
       <c r="I15" s="1">
-        <v>1163.0</v>
+        <v>1163</v>
       </c>
       <c r="J15" s="1">
-        <v>1039.0</v>
+        <v>1039</v>
       </c>
       <c r="K15" s="1">
-        <v>943.0</v>
+        <v>943</v>
       </c>
       <c r="L15" s="1">
-        <v>851.0</v>
+        <v>851</v>
       </c>
       <c r="M15" s="1">
-        <v>786.0</v>
+        <v>786</v>
       </c>
       <c r="N15" s="1">
-        <v>718.0</v>
+        <v>718</v>
       </c>
       <c r="O15" s="1">
-        <v>647.0</v>
+        <v>647</v>
       </c>
       <c r="P15" s="1">
-        <v>605.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1">
-        <v>3655.0</v>
+        <v>3655</v>
       </c>
       <c r="D16" s="1">
-        <v>2757.0</v>
+        <v>2757</v>
       </c>
       <c r="E16" s="1">
-        <v>2154.0</v>
+        <v>2154</v>
       </c>
       <c r="F16" s="1">
-        <v>1759.0</v>
+        <v>1759</v>
       </c>
       <c r="G16" s="1">
-        <v>1526.0</v>
+        <v>1526</v>
       </c>
       <c r="H16" s="1">
-        <v>1337.0</v>
+        <v>1337</v>
       </c>
       <c r="I16" s="1">
-        <v>1170.0</v>
+        <v>1170</v>
       </c>
       <c r="J16" s="1">
-        <v>1036.0</v>
+        <v>1036</v>
       </c>
       <c r="K16" s="1">
-        <v>940.0</v>
+        <v>940</v>
       </c>
       <c r="L16" s="1">
-        <v>845.0</v>
+        <v>845</v>
       </c>
       <c r="M16" s="1">
-        <v>781.0</v>
+        <v>781</v>
       </c>
       <c r="N16" s="1">
-        <v>716.0</v>
+        <v>716</v>
       </c>
       <c r="O16" s="1">
-        <v>643.0</v>
+        <v>643</v>
       </c>
       <c r="P16" s="1">
-        <v>607.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C17" s="1">
-        <v>3656.0</v>
+        <v>3656</v>
       </c>
       <c r="D17" s="1">
-        <v>2751.0</v>
+        <v>2751</v>
       </c>
       <c r="E17" s="1">
-        <v>2158.0</v>
+        <v>2158</v>
       </c>
       <c r="F17" s="1">
-        <v>1754.0</v>
+        <v>1754</v>
       </c>
       <c r="G17" s="1">
-        <v>1516.0</v>
+        <v>1516</v>
       </c>
       <c r="H17" s="1">
-        <v>1335.0</v>
+        <v>1335</v>
       </c>
       <c r="I17" s="1">
-        <v>1164.0</v>
+        <v>1164</v>
       </c>
       <c r="J17" s="1">
-        <v>1036.0</v>
+        <v>1036</v>
       </c>
       <c r="K17" s="1">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="L17" s="1">
-        <v>843.0</v>
+        <v>843</v>
       </c>
       <c r="M17" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="N17" s="1">
-        <v>712.0</v>
+        <v>712</v>
       </c>
       <c r="O17" s="1">
-        <v>649.0</v>
+        <v>649</v>
       </c>
       <c r="P17" s="1">
-        <v>616.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C18" s="3">
-        <f t="shared" ref="C18:M18" si="4">STDEV(C15:C17)</f>
-        <v>2.081665999</v>
+        <f t="shared" ref="C18:M18" si="3">STDEV(C15:C17)</f>
+        <v>2.0816659994661326</v>
       </c>
       <c r="D18" s="3">
-        <f t="shared" si="4"/>
-        <v>3.055050463</v>
+        <f t="shared" si="3"/>
+        <v>3.0550504633038931</v>
       </c>
       <c r="E18" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="F18" s="3">
-        <f t="shared" si="4"/>
-        <v>2.645751311</v>
+        <f t="shared" si="3"/>
+        <v>2.6457513110645907</v>
       </c>
       <c r="G18" s="3">
-        <f t="shared" si="4"/>
-        <v>5.507570547</v>
+        <f t="shared" si="3"/>
+        <v>5.5075705472861021</v>
       </c>
       <c r="H18" s="3">
-        <f t="shared" si="4"/>
-        <v>5.859465277</v>
+        <f t="shared" si="3"/>
+        <v>5.8594652770823146</v>
       </c>
       <c r="I18" s="3">
-        <f t="shared" si="4"/>
-        <v>3.785938897</v>
+        <f t="shared" si="3"/>
+        <v>3.7859388972001824</v>
       </c>
       <c r="J18" s="3">
-        <f t="shared" si="4"/>
-        <v>1.732050808</v>
+        <f t="shared" si="3"/>
+        <v>1.7320508075688772</v>
       </c>
       <c r="K18" s="3">
-        <f t="shared" si="4"/>
-        <v>2.081665999</v>
+        <f t="shared" si="3"/>
+        <v>2.0816659994661331</v>
       </c>
       <c r="L18" s="3">
-        <f t="shared" si="4"/>
-        <v>4.163331999</v>
+        <f t="shared" si="3"/>
+        <v>4.1633319989322652</v>
       </c>
       <c r="M18" s="3">
-        <f t="shared" si="4"/>
-        <v>2.645751311</v>
+        <f t="shared" si="3"/>
+        <v>2.6457513110645907</v>
       </c>
       <c r="N18" s="3">
         <f>STDEV(O15:O17)</f>
-        <v>3.055050463</v>
+        <v>3.0550504633038931</v>
       </c>
       <c r="O18" s="3">
-        <f t="shared" ref="O18:P18" si="5">STDEV(O15:O17)</f>
-        <v>3.055050463</v>
+        <f t="shared" ref="O18:P18" si="4">STDEV(O15:O17)</f>
+        <v>3.0550504633038931</v>
       </c>
       <c r="P18" s="3">
-        <f t="shared" si="5"/>
-        <v>5.859465277</v>
+        <f t="shared" si="4"/>
+        <v>5.8594652770823146</v>
       </c>
       <c r="Q18" s="3">
         <f>AVERAGE(C18:P18)</f>
-        <v>3.394843487</v>
+        <v>3.3948434868660846</v>
       </c>
       <c r="R18" s="1">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1">
-        <v>3843.0</v>
+        <v>3957</v>
       </c>
       <c r="D19" s="1">
-        <v>2918.0</v>
+        <v>2801</v>
       </c>
       <c r="E19" s="1">
-        <v>2279.0</v>
+        <v>2215</v>
       </c>
       <c r="F19" s="1">
-        <v>1875.0</v>
+        <v>1779</v>
       </c>
       <c r="G19" s="1">
-        <v>1596.0</v>
+        <v>1557</v>
       </c>
       <c r="H19" s="1">
-        <v>1419.0</v>
+        <v>1367</v>
       </c>
       <c r="I19" s="1">
-        <v>1274.0</v>
+        <v>1240</v>
       </c>
       <c r="J19" s="1">
-        <v>1165.0</v>
+        <v>1139</v>
       </c>
       <c r="K19" s="1">
-        <v>1102.0</v>
+        <v>1074</v>
       </c>
       <c r="L19" s="1">
-        <v>1032.0</v>
+        <v>1010</v>
       </c>
       <c r="M19" s="1">
-        <v>968.0</v>
+        <v>977</v>
       </c>
       <c r="N19" s="1">
-        <v>935.0</v>
+        <v>946</v>
       </c>
       <c r="O19" s="1">
-        <v>903.0</v>
+        <v>914</v>
       </c>
       <c r="P19" s="1">
-        <v>871.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C20" s="1">
-        <v>3846.0</v>
+        <v>3956</v>
       </c>
       <c r="D20" s="1">
-        <v>2917.0</v>
+        <v>2800</v>
       </c>
       <c r="E20" s="1">
-        <v>2279.0</v>
+        <v>2216</v>
       </c>
       <c r="F20" s="1">
-        <v>1875.0</v>
+        <v>1780</v>
       </c>
       <c r="G20" s="1">
-        <v>1597.0</v>
+        <v>1558</v>
       </c>
       <c r="H20" s="1">
-        <v>1419.0</v>
+        <v>1367</v>
       </c>
       <c r="I20" s="1">
-        <v>1284.0</v>
+        <v>1240</v>
       </c>
       <c r="J20" s="1">
-        <v>1165.0</v>
+        <v>1138</v>
       </c>
       <c r="K20" s="1">
-        <v>1102.0</v>
+        <v>1074</v>
       </c>
       <c r="L20" s="1">
-        <v>1032.0</v>
+        <v>1009</v>
       </c>
       <c r="M20" s="1">
-        <v>967.0</v>
+        <v>978</v>
       </c>
       <c r="N20" s="1">
-        <v>936.0</v>
+        <v>945</v>
       </c>
       <c r="O20" s="1">
-        <v>903.0</v>
+        <v>914</v>
       </c>
       <c r="P20" s="1">
-        <v>871.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1">
-        <v>3845.0</v>
+        <v>3957</v>
       </c>
       <c r="D21" s="1">
-        <v>2917.0</v>
+        <v>2802</v>
       </c>
       <c r="E21" s="1">
-        <v>2278.0</v>
+        <v>2216</v>
       </c>
       <c r="F21" s="1">
-        <v>1875.0</v>
+        <v>1779</v>
       </c>
       <c r="G21" s="1">
-        <v>1596.0</v>
+        <v>1558</v>
       </c>
       <c r="H21" s="1">
-        <v>1418.0</v>
+        <v>1368</v>
       </c>
       <c r="I21" s="1">
-        <v>1276.0</v>
+        <v>1239</v>
       </c>
       <c r="J21" s="1">
-        <v>1164.0</v>
+        <v>1139</v>
       </c>
       <c r="K21" s="1">
-        <v>1102.0</v>
+        <v>1073</v>
       </c>
       <c r="L21" s="1">
-        <v>1031.0</v>
+        <v>1011</v>
       </c>
       <c r="M21" s="1">
-        <v>967.0</v>
+        <v>977</v>
       </c>
       <c r="N21" s="1">
-        <v>935.0</v>
+        <v>947</v>
       </c>
       <c r="O21" s="1">
-        <v>904.0</v>
+        <v>915</v>
       </c>
       <c r="P21" s="1">
-        <v>871.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C22" s="3">
-        <f t="shared" ref="C22:P22" si="6">STDEV(C19:C21)</f>
-        <v>1.527525232</v>
+        <f t="shared" ref="C22:P22" si="5">STDEV(C19:C21)</f>
+        <v>0.57735026918962584</v>
       </c>
       <c r="D22" s="3">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="E22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="F22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="G22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="H22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="I22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="J22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="K22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="L22" s="3">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="M22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962573</v>
+      </c>
+      <c r="N22" s="3">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="O22" s="3">
+        <f t="shared" si="5"/>
+        <v>0.57735026918962573</v>
+      </c>
+      <c r="P22" s="3">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="Q22" s="3">
+        <f>AVERAGE(C22:P22)</f>
+        <v>0.69810733513544698</v>
+      </c>
+      <c r="R22" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>6</v>
+      </c>
+      <c r="B23" s="1">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1">
+        <v>3956</v>
+      </c>
+      <c r="D23" s="1">
+        <v>2888</v>
+      </c>
+      <c r="E23" s="1">
+        <v>2302</v>
+      </c>
+      <c r="F23" s="1">
+        <v>1866</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1612</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1422</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1295</v>
+      </c>
+      <c r="J23" s="1">
+        <v>1199</v>
+      </c>
+      <c r="K23" s="1">
+        <v>1096</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M23" s="1">
+        <v>976</v>
+      </c>
+      <c r="N23" s="1">
+        <v>936</v>
+      </c>
+      <c r="O23" s="1">
+        <v>904</v>
+      </c>
+      <c r="P23" s="1">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B24" s="1">
+        <v>2</v>
+      </c>
+      <c r="C24" s="1">
+        <v>3955</v>
+      </c>
+      <c r="D24" s="1">
+        <v>2896</v>
+      </c>
+      <c r="E24" s="1">
+        <v>2302</v>
+      </c>
+      <c r="F24" s="1">
+        <v>1865</v>
+      </c>
+      <c r="G24" s="1">
+        <v>1612</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1421</v>
+      </c>
+      <c r="I24" s="1">
+        <v>1295</v>
+      </c>
+      <c r="J24" s="1">
+        <v>1199</v>
+      </c>
+      <c r="K24" s="1">
+        <v>1096</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M24" s="1">
+        <v>972</v>
+      </c>
+      <c r="N24" s="1">
+        <v>936</v>
+      </c>
+      <c r="O24" s="1">
+        <v>904</v>
+      </c>
+      <c r="P24" s="1">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B25" s="1">
+        <v>3</v>
+      </c>
+      <c r="C25" s="1">
+        <v>3956</v>
+      </c>
+      <c r="D25" s="1">
+        <v>2887</v>
+      </c>
+      <c r="E25" s="1">
+        <v>2301</v>
+      </c>
+      <c r="F25" s="1">
+        <v>1866</v>
+      </c>
+      <c r="G25" s="1">
+        <v>1612</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1422</v>
+      </c>
+      <c r="I25" s="1">
+        <v>1295</v>
+      </c>
+      <c r="J25" s="1">
+        <v>1199</v>
+      </c>
+      <c r="K25" s="1">
+        <v>1097</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1000</v>
+      </c>
+      <c r="M25" s="1">
+        <v>974</v>
+      </c>
+      <c r="N25" s="1">
+        <v>935</v>
+      </c>
+      <c r="O25" s="1">
+        <v>904</v>
+      </c>
+      <c r="P25" s="1">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="C26" s="3">
+        <f t="shared" ref="C26:P26" si="6">STDEV(C23:C25)</f>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="D26" s="3">
         <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="E22" s="3">
+        <v>4.932882862316248</v>
+      </c>
+      <c r="E26" s="3">
         <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="F22" s="3">
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="F26" s="3">
+        <f t="shared" si="6"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="G26" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H26" s="3">
         <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="H22" s="3">
-        <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="I22" s="3">
-        <f t="shared" si="6"/>
-        <v>5.291502622</v>
-      </c>
-      <c r="J22" s="3">
-        <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="K22" s="3">
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="I26" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="L22" s="3">
-        <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="M22" s="3">
-        <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="N22" s="3">
-        <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="O22" s="3">
-        <f t="shared" si="6"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="P22" s="3">
+      <c r="J26" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Q22" s="3">
-        <f>AVERAGE(C22:P22)</f>
-        <v>0.8582271626</v>
-      </c>
-      <c r="R22" s="1">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1">
-        <v>6.0</v>
-      </c>
-      <c r="B23" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="C23" s="1">
-        <v>3956.0</v>
-      </c>
-      <c r="D23" s="1">
-        <v>2888.0</v>
-      </c>
-      <c r="E23" s="1">
-        <v>2302.0</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1866.0</v>
-      </c>
-      <c r="G23" s="1">
-        <v>1612.0</v>
-      </c>
-      <c r="H23" s="1">
-        <v>1422.0</v>
-      </c>
-      <c r="I23" s="1">
-        <v>1295.0</v>
-      </c>
-      <c r="J23" s="1">
-        <v>1199.0</v>
-      </c>
-      <c r="K23" s="1">
-        <v>1096.0</v>
-      </c>
-      <c r="L23" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="M23" s="1">
-        <v>976.0</v>
-      </c>
-      <c r="N23" s="1">
-        <v>936.0</v>
-      </c>
-      <c r="O23" s="1">
-        <v>904.0</v>
-      </c>
-      <c r="P23" s="1">
-        <v>872.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="1">
-        <v>2.0</v>
-      </c>
-      <c r="C24" s="1">
-        <v>3955.0</v>
-      </c>
-      <c r="D24" s="1">
-        <v>2896.0</v>
-      </c>
-      <c r="E24" s="1">
-        <v>2302.0</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1865.0</v>
-      </c>
-      <c r="G24" s="1">
-        <v>1612.0</v>
-      </c>
-      <c r="H24" s="1">
-        <v>1421.0</v>
-      </c>
-      <c r="I24" s="1">
-        <v>1295.0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>1199.0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>1096.0</v>
-      </c>
-      <c r="L24" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="M24" s="1">
-        <v>972.0</v>
-      </c>
-      <c r="N24" s="1">
-        <v>936.0</v>
-      </c>
-      <c r="O24" s="1">
-        <v>904.0</v>
-      </c>
-      <c r="P24" s="1">
-        <v>872.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="C25" s="1">
-        <v>3956.0</v>
-      </c>
-      <c r="D25" s="1">
-        <v>2887.0</v>
-      </c>
-      <c r="E25" s="1">
-        <v>2301.0</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1866.0</v>
-      </c>
-      <c r="G25" s="1">
-        <v>1612.0</v>
-      </c>
-      <c r="H25" s="1">
-        <v>1422.0</v>
-      </c>
-      <c r="I25" s="1">
-        <v>1295.0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>1199.0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>1097.0</v>
-      </c>
-      <c r="L25" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>974.0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>935.0</v>
-      </c>
-      <c r="O25" s="1">
-        <v>904.0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>872.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="C26" s="3">
-        <f t="shared" ref="C26:P26" si="7">STDEV(C23:C25)</f>
-        <v>0.5773502692</v>
-      </c>
-      <c r="D26" s="3">
-        <f t="shared" si="7"/>
-        <v>4.932882862</v>
-      </c>
-      <c r="E26" s="3">
-        <f t="shared" si="7"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="F26" s="3">
-        <f t="shared" si="7"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="G26" s="3">
-        <f t="shared" si="7"/>
+      <c r="K26" s="3">
+        <f t="shared" si="6"/>
+        <v>0.57735026918962584</v>
+      </c>
+      <c r="L26" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H26" s="3">
-        <f t="shared" si="7"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="I26" s="3">
-        <f t="shared" si="7"/>
+      <c r="M26" s="3">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="N26" s="3">
+        <f t="shared" si="6"/>
+        <v>0.57735026918962573</v>
+      </c>
+      <c r="O26" s="3">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="J26" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <f t="shared" si="7"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="L26" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
-        <f t="shared" si="7"/>
-        <v>2</v>
-      </c>
-      <c r="N26" s="3">
-        <f t="shared" si="7"/>
-        <v>0.5773502692</v>
-      </c>
-      <c r="O26" s="3">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
       <c r="P26" s="3">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="Q26" s="3">
         <f>AVERAGE(C26:P26)</f>
-        <v>0.7426417484</v>
+        <v>0.74264174838957175</v>
       </c>
       <c r="R26" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.75"/>
+  <dimension ref="A1:R26"/>
+  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="3" max="22" width="8.14"/>
+    <col min="3" max="22" width="8.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -2182,1241 +2399,1243 @@
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
     </row>
-    <row r="2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C2" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D2" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F2" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G2" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="H2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J2" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L2" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="M2" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="N2" s="2">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="O2" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="P2" s="2">
-        <v>30.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>3608.0</v>
+        <v>3608</v>
       </c>
       <c r="D3" s="1">
-        <v>2706.0</v>
+        <v>2706</v>
       </c>
       <c r="E3" s="1">
-        <v>2149.0</v>
+        <v>2149</v>
       </c>
       <c r="F3" s="1">
-        <v>1780.0</v>
+        <v>1780</v>
       </c>
       <c r="G3" s="1">
-        <v>1526.0</v>
+        <v>1526</v>
       </c>
       <c r="H3" s="1">
-        <v>1335.0</v>
+        <v>1335</v>
       </c>
       <c r="I3" s="1">
-        <v>1167.0</v>
+        <v>1167</v>
       </c>
       <c r="J3" s="1">
-        <v>1040.0</v>
+        <v>1040</v>
       </c>
       <c r="K3" s="1">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="L3" s="1">
-        <v>848.0</v>
+        <v>848</v>
       </c>
       <c r="M3" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="N3" s="1">
-        <v>711.0</v>
+        <v>711</v>
       </c>
       <c r="O3" s="1">
-        <v>647.0</v>
+        <v>647</v>
       </c>
       <c r="P3" s="1">
-        <v>582.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C4" s="1">
-        <v>3608.0</v>
+        <v>3608</v>
       </c>
       <c r="D4" s="1">
-        <v>2706.0</v>
+        <v>2706</v>
       </c>
       <c r="E4" s="1">
-        <v>2147.0</v>
+        <v>2147</v>
       </c>
       <c r="F4" s="1">
-        <v>1781.0</v>
+        <v>1781</v>
       </c>
       <c r="G4" s="1">
-        <v>1526.0</v>
+        <v>1526</v>
       </c>
       <c r="H4" s="1">
-        <v>1336.0</v>
+        <v>1336</v>
       </c>
       <c r="I4" s="1">
-        <v>1167.0</v>
+        <v>1167</v>
       </c>
       <c r="J4" s="1">
-        <v>1040.0</v>
+        <v>1040</v>
       </c>
       <c r="K4" s="1">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="L4" s="1">
-        <v>848.0</v>
+        <v>848</v>
       </c>
       <c r="M4" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="N4" s="1">
-        <v>711.0</v>
+        <v>711</v>
       </c>
       <c r="O4" s="1">
-        <v>647.0</v>
+        <v>647</v>
       </c>
       <c r="P4" s="1">
-        <v>582.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C5" s="1">
-        <v>3609.0</v>
+        <v>3609</v>
       </c>
       <c r="D5" s="1">
-        <v>2705.0</v>
+        <v>2705</v>
       </c>
       <c r="E5" s="1">
-        <v>2141.0</v>
+        <v>2141</v>
       </c>
       <c r="F5" s="1">
-        <v>1780.0</v>
+        <v>1780</v>
       </c>
       <c r="G5" s="1">
-        <v>1526.0</v>
+        <v>1526</v>
       </c>
       <c r="H5" s="1">
-        <v>1335.0</v>
+        <v>1335</v>
       </c>
       <c r="I5" s="1">
-        <v>1167.0</v>
+        <v>1167</v>
       </c>
       <c r="J5" s="1">
-        <v>1040.0</v>
+        <v>1040</v>
       </c>
       <c r="K5" s="1">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="L5" s="1">
-        <v>847.0</v>
+        <v>847</v>
       </c>
       <c r="M5" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="N5" s="1">
-        <v>711.0</v>
+        <v>711</v>
       </c>
       <c r="O5" s="1">
-        <v>646.0</v>
+        <v>646</v>
       </c>
       <c r="P5" s="1">
-        <v>603.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C6" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D6" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F6" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="H6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J6" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K6" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L6" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="M6" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="N6" s="2">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="O6" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="P6" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="Q6" s="4">
         <f>AVERAGE(C6:P6)</f>
         <v>17</v>
       </c>
       <c r="R6" s="1">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>3901.0</v>
+        <v>3901</v>
       </c>
       <c r="D7" s="1">
-        <v>2876.0</v>
+        <v>2876</v>
       </c>
       <c r="E7" s="1">
-        <v>2257.0</v>
+        <v>2257</v>
       </c>
       <c r="F7" s="1">
-        <v>1883.0</v>
+        <v>1883</v>
       </c>
       <c r="G7" s="1">
-        <v>1604.0</v>
+        <v>1604</v>
       </c>
       <c r="H7" s="1">
-        <v>1378.0</v>
+        <v>1378</v>
       </c>
       <c r="I7" s="1">
-        <v>1218.0</v>
+        <v>1218</v>
       </c>
       <c r="J7" s="1">
-        <v>1091.0</v>
+        <v>1091</v>
       </c>
       <c r="K7" s="1">
-        <v>965.0</v>
+        <v>965</v>
       </c>
       <c r="L7" s="1">
-        <v>906.0</v>
+        <v>906</v>
       </c>
       <c r="M7" s="1">
-        <v>793.0</v>
+        <v>793</v>
       </c>
       <c r="N7" s="1">
-        <v>731.0</v>
+        <v>731</v>
       </c>
       <c r="O7" s="1">
-        <v>663.0</v>
+        <v>663</v>
       </c>
       <c r="P7" s="1">
-        <v>611.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C8" s="1">
-        <v>3900.0</v>
+        <v>3900</v>
       </c>
       <c r="D8" s="1">
-        <v>2877.0</v>
+        <v>2877</v>
       </c>
       <c r="E8" s="1">
-        <v>2260.0</v>
+        <v>2260</v>
       </c>
       <c r="F8" s="1">
-        <v>1881.0</v>
+        <v>1881</v>
       </c>
       <c r="G8" s="1">
-        <v>1602.0</v>
+        <v>1602</v>
       </c>
       <c r="H8" s="1">
-        <v>1379.0</v>
+        <v>1379</v>
       </c>
       <c r="I8" s="1">
-        <v>1216.0</v>
+        <v>1216</v>
       </c>
       <c r="J8" s="1">
-        <v>1095.0</v>
+        <v>1095</v>
       </c>
       <c r="K8" s="1">
-        <v>964.0</v>
+        <v>964</v>
       </c>
       <c r="L8" s="1">
-        <v>889.0</v>
+        <v>889</v>
       </c>
       <c r="M8" s="1">
-        <v>794.0</v>
+        <v>794</v>
       </c>
       <c r="N8" s="1">
-        <v>728.0</v>
+        <v>728</v>
       </c>
       <c r="O8" s="1">
-        <v>665.0</v>
+        <v>665</v>
       </c>
       <c r="P8" s="1">
-        <v>604.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C9" s="1">
-        <v>3901.0</v>
+        <v>3901</v>
       </c>
       <c r="D9" s="1">
-        <v>2880.0</v>
+        <v>2880</v>
       </c>
       <c r="E9" s="1">
-        <v>2260.0</v>
+        <v>2260</v>
       </c>
       <c r="F9" s="1">
-        <v>1881.0</v>
+        <v>1881</v>
       </c>
       <c r="G9" s="1">
-        <v>1603.0</v>
+        <v>1603</v>
       </c>
       <c r="H9" s="1">
-        <v>1378.0</v>
+        <v>1378</v>
       </c>
       <c r="I9" s="1">
-        <v>1219.0</v>
+        <v>1219</v>
       </c>
       <c r="J9" s="1">
-        <v>1095.0</v>
+        <v>1095</v>
       </c>
       <c r="K9" s="1">
-        <v>967.0</v>
+        <v>967</v>
       </c>
       <c r="L9" s="1">
-        <v>905.0</v>
+        <v>905</v>
       </c>
       <c r="M9" s="1">
-        <v>794.0</v>
+        <v>794</v>
       </c>
       <c r="N9" s="1">
-        <v>732.0</v>
+        <v>732</v>
       </c>
       <c r="O9" s="1">
-        <v>668.0</v>
+        <v>668</v>
       </c>
       <c r="P9" s="1">
-        <v>629.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C10" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D10" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E10" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F10" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G10" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I10" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J10" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K10" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L10" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="M10" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="N10" s="2">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="O10" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="P10" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="Q10" s="4">
         <f>AVERAGE(C10:P10)</f>
         <v>17</v>
       </c>
       <c r="R10" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="B11" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="1">
-        <v>4085.0</v>
+        <v>4085</v>
       </c>
       <c r="D11" s="1">
-        <v>3012.0</v>
+        <v>3012</v>
       </c>
       <c r="E11" s="1">
-        <v>2340.0</v>
+        <v>2340</v>
       </c>
       <c r="F11" s="1">
-        <v>1907.0</v>
+        <v>1907</v>
       </c>
       <c r="G11" s="1">
-        <v>1641.0</v>
+        <v>1641</v>
       </c>
       <c r="H11" s="1">
-        <v>1420.0</v>
+        <v>1420</v>
       </c>
       <c r="I11" s="1">
-        <v>1229.0</v>
+        <v>1229</v>
       </c>
       <c r="J11" s="1">
-        <v>1091.0</v>
+        <v>1091</v>
       </c>
       <c r="K11" s="1">
-        <v>991.0</v>
+        <v>991</v>
       </c>
       <c r="L11" s="1">
-        <v>896.0</v>
+        <v>896</v>
       </c>
       <c r="M11" s="1">
-        <v>803.0</v>
+        <v>803</v>
       </c>
       <c r="N11" s="1">
-        <v>739.0</v>
+        <v>739</v>
       </c>
       <c r="O11" s="1">
-        <v>675.0</v>
+        <v>675</v>
       </c>
       <c r="P11" s="1">
-        <v>608.0</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B12" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C12" s="1">
-        <v>4085.0</v>
+        <v>4085</v>
       </c>
       <c r="D12" s="1">
-        <v>3012.0</v>
+        <v>3012</v>
       </c>
       <c r="E12" s="1">
-        <v>2341.0</v>
+        <v>2341</v>
       </c>
       <c r="F12" s="1">
-        <v>1907.0</v>
+        <v>1907</v>
       </c>
       <c r="G12" s="1">
-        <v>1641.0</v>
+        <v>1641</v>
       </c>
       <c r="H12" s="1">
-        <v>1421.0</v>
+        <v>1421</v>
       </c>
       <c r="I12" s="1">
-        <v>1229.0</v>
+        <v>1229</v>
       </c>
       <c r="J12" s="1">
-        <v>1091.0</v>
+        <v>1091</v>
       </c>
       <c r="K12" s="1">
-        <v>991.0</v>
+        <v>991</v>
       </c>
       <c r="L12" s="1">
-        <v>896.0</v>
+        <v>896</v>
       </c>
       <c r="M12" s="1">
-        <v>803.0</v>
+        <v>803</v>
       </c>
       <c r="N12" s="1">
-        <v>739.0</v>
+        <v>739</v>
       </c>
       <c r="O12" s="1">
-        <v>675.0</v>
+        <v>675</v>
       </c>
       <c r="P12" s="1">
-        <v>608.0</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B13" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C13" s="1">
-        <v>4086.0</v>
+        <v>4086</v>
       </c>
       <c r="D13" s="1">
-        <v>3012.0</v>
+        <v>3012</v>
       </c>
       <c r="E13" s="1">
-        <v>2340.0</v>
+        <v>2340</v>
       </c>
       <c r="F13" s="1">
-        <v>1907.0</v>
+        <v>1907</v>
       </c>
       <c r="G13" s="1">
-        <v>1641.0</v>
+        <v>1641</v>
       </c>
       <c r="H13" s="1">
-        <v>1420.0</v>
+        <v>1420</v>
       </c>
       <c r="I13" s="1">
-        <v>1229.0</v>
+        <v>1229</v>
       </c>
       <c r="J13" s="1">
-        <v>1091.0</v>
+        <v>1091</v>
       </c>
       <c r="K13" s="1">
-        <v>991.0</v>
+        <v>991</v>
       </c>
       <c r="L13" s="1">
-        <v>870.0</v>
+        <v>870</v>
       </c>
       <c r="M13" s="1">
-        <v>803.0</v>
+        <v>803</v>
       </c>
       <c r="N13" s="1">
-        <v>739.0</v>
+        <v>739</v>
       </c>
       <c r="O13" s="1">
-        <v>675.0</v>
+        <v>675</v>
       </c>
       <c r="P13" s="1">
-        <v>608.0</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C14" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D14" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E14" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G14" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="H14" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I14" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J14" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K14" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L14" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="M14" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="N14" s="2">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="O14" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="P14" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="Q14" s="4">
         <f>AVERAGE(C14:P14)</f>
         <v>17</v>
       </c>
       <c r="R14" s="1">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="B15" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="1">
-        <v>3659.0</v>
+        <v>3659</v>
       </c>
       <c r="D15" s="1">
-        <v>2755.0</v>
+        <v>2755</v>
       </c>
       <c r="E15" s="1">
-        <v>2156.0</v>
+        <v>2156</v>
       </c>
       <c r="F15" s="1">
-        <v>1758.0</v>
+        <v>1758</v>
       </c>
       <c r="G15" s="1">
-        <v>1525.0</v>
+        <v>1525</v>
       </c>
       <c r="H15" s="1">
-        <v>1326.0</v>
+        <v>1326</v>
       </c>
       <c r="I15" s="1">
-        <v>1163.0</v>
+        <v>1163</v>
       </c>
       <c r="J15" s="1">
-        <v>1039.0</v>
+        <v>1039</v>
       </c>
       <c r="K15" s="1">
-        <v>943.0</v>
+        <v>943</v>
       </c>
       <c r="L15" s="1">
-        <v>851.0</v>
+        <v>851</v>
       </c>
       <c r="M15" s="1">
-        <v>786.0</v>
+        <v>786</v>
       </c>
       <c r="N15" s="1">
-        <v>718.0</v>
+        <v>718</v>
       </c>
       <c r="O15" s="1">
-        <v>647.0</v>
+        <v>647</v>
       </c>
       <c r="P15" s="1">
-        <v>605.0</v>
-      </c>
-    </row>
-    <row r="16">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C16" s="1">
-        <v>3655.0</v>
+        <v>3655</v>
       </c>
       <c r="D16" s="1">
-        <v>2757.0</v>
+        <v>2757</v>
       </c>
       <c r="E16" s="1">
-        <v>2154.0</v>
+        <v>2154</v>
       </c>
       <c r="F16" s="1">
-        <v>1759.0</v>
+        <v>1759</v>
       </c>
       <c r="G16" s="1">
-        <v>1526.0</v>
+        <v>1526</v>
       </c>
       <c r="H16" s="1">
-        <v>1337.0</v>
+        <v>1337</v>
       </c>
       <c r="I16" s="1">
-        <v>1170.0</v>
+        <v>1170</v>
       </c>
       <c r="J16" s="1">
-        <v>1036.0</v>
+        <v>1036</v>
       </c>
       <c r="K16" s="1">
-        <v>940.0</v>
+        <v>940</v>
       </c>
       <c r="L16" s="1">
-        <v>845.0</v>
+        <v>845</v>
       </c>
       <c r="M16" s="1">
-        <v>781.0</v>
+        <v>781</v>
       </c>
       <c r="N16" s="1">
-        <v>716.0</v>
+        <v>716</v>
       </c>
       <c r="O16" s="1">
-        <v>643.0</v>
+        <v>643</v>
       </c>
       <c r="P16" s="1">
-        <v>607.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C17" s="1">
-        <v>3656.0</v>
+        <v>3656</v>
       </c>
       <c r="D17" s="1">
-        <v>2751.0</v>
+        <v>2751</v>
       </c>
       <c r="E17" s="1">
-        <v>2158.0</v>
+        <v>2158</v>
       </c>
       <c r="F17" s="1">
-        <v>1754.0</v>
+        <v>1754</v>
       </c>
       <c r="G17" s="1">
-        <v>1516.0</v>
+        <v>1516</v>
       </c>
       <c r="H17" s="1">
-        <v>1335.0</v>
+        <v>1335</v>
       </c>
       <c r="I17" s="1">
-        <v>1164.0</v>
+        <v>1164</v>
       </c>
       <c r="J17" s="1">
-        <v>1036.0</v>
+        <v>1036</v>
       </c>
       <c r="K17" s="1">
-        <v>944.0</v>
+        <v>944</v>
       </c>
       <c r="L17" s="1">
-        <v>843.0</v>
+        <v>843</v>
       </c>
       <c r="M17" s="1">
-        <v>785.0</v>
+        <v>785</v>
       </c>
       <c r="N17" s="1">
-        <v>712.0</v>
+        <v>712</v>
       </c>
       <c r="O17" s="1">
-        <v>649.0</v>
+        <v>649</v>
       </c>
       <c r="P17" s="1">
-        <v>616.0</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C18" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D18" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E18" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F18" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G18" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="H18" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I18" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J18" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K18" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L18" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="M18" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="N18" s="2">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="O18" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="P18" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="Q18" s="4">
         <f>AVERAGE(C18:P18)</f>
         <v>17</v>
       </c>
       <c r="R18" s="1">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="B19" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C19" s="1">
-        <v>3843.0</v>
+        <v>3957</v>
       </c>
       <c r="D19" s="1">
-        <v>2918.0</v>
+        <v>2801</v>
       </c>
       <c r="E19" s="1">
-        <v>2279.0</v>
+        <v>2215</v>
       </c>
       <c r="F19" s="1">
-        <v>1875.0</v>
+        <v>1779</v>
       </c>
       <c r="G19" s="1">
-        <v>1596.0</v>
+        <v>1557</v>
       </c>
       <c r="H19" s="1">
-        <v>1419.0</v>
+        <v>1367</v>
       </c>
       <c r="I19" s="1">
-        <v>1274.0</v>
+        <v>1240</v>
       </c>
       <c r="J19" s="1">
-        <v>1165.0</v>
+        <v>1139</v>
       </c>
       <c r="K19" s="1">
-        <v>1102.0</v>
+        <v>1074</v>
       </c>
       <c r="L19" s="1">
-        <v>1032.0</v>
+        <v>1010</v>
       </c>
       <c r="M19" s="1">
-        <v>968.0</v>
+        <v>977</v>
       </c>
       <c r="N19" s="1">
-        <v>935.0</v>
+        <v>946</v>
       </c>
       <c r="O19" s="1">
-        <v>903.0</v>
+        <v>914</v>
       </c>
       <c r="P19" s="1">
-        <v>871.0</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C20" s="1">
-        <v>3846.0</v>
+        <v>3956</v>
       </c>
       <c r="D20" s="1">
-        <v>2917.0</v>
+        <v>2800</v>
       </c>
       <c r="E20" s="1">
-        <v>2279.0</v>
+        <v>2216</v>
       </c>
       <c r="F20" s="1">
-        <v>1875.0</v>
+        <v>1780</v>
       </c>
       <c r="G20" s="1">
-        <v>1597.0</v>
+        <v>1558</v>
       </c>
       <c r="H20" s="1">
-        <v>1419.0</v>
+        <v>1367</v>
       </c>
       <c r="I20" s="1">
-        <v>1284.0</v>
+        <v>1240</v>
       </c>
       <c r="J20" s="1">
-        <v>1165.0</v>
+        <v>1138</v>
       </c>
       <c r="K20" s="1">
-        <v>1102.0</v>
+        <v>1074</v>
       </c>
       <c r="L20" s="1">
-        <v>1032.0</v>
+        <v>1009</v>
       </c>
       <c r="M20" s="1">
-        <v>967.0</v>
+        <v>978</v>
       </c>
       <c r="N20" s="1">
-        <v>936.0</v>
+        <v>945</v>
       </c>
       <c r="O20" s="1">
-        <v>903.0</v>
+        <v>914</v>
       </c>
       <c r="P20" s="1">
-        <v>871.0</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C21" s="1">
-        <v>3845.0</v>
+        <v>3957</v>
       </c>
       <c r="D21" s="1">
-        <v>2917.0</v>
+        <v>2802</v>
       </c>
       <c r="E21" s="1">
-        <v>2278.0</v>
+        <v>2216</v>
       </c>
       <c r="F21" s="1">
-        <v>1875.0</v>
+        <v>1779</v>
       </c>
       <c r="G21" s="1">
-        <v>1596.0</v>
+        <v>1558</v>
       </c>
       <c r="H21" s="1">
-        <v>1418.0</v>
+        <v>1368</v>
       </c>
       <c r="I21" s="1">
-        <v>1276.0</v>
+        <v>1239</v>
       </c>
       <c r="J21" s="1">
-        <v>1164.0</v>
+        <v>1139</v>
       </c>
       <c r="K21" s="1">
-        <v>1102.0</v>
+        <v>1073</v>
       </c>
       <c r="L21" s="1">
-        <v>1031.0</v>
+        <v>1011</v>
       </c>
       <c r="M21" s="1">
-        <v>967.0</v>
+        <v>977</v>
       </c>
       <c r="N21" s="1">
-        <v>935.0</v>
+        <v>947</v>
       </c>
       <c r="O21" s="1">
-        <v>904.0</v>
+        <v>915</v>
       </c>
       <c r="P21" s="1">
-        <v>871.0</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C22" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="D22" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="E22" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="F22" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="G22" s="2">
-        <v>12.0</v>
+        <v>12</v>
       </c>
       <c r="H22" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I22" s="2">
-        <v>16.0</v>
+        <v>16</v>
       </c>
       <c r="J22" s="2">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="K22" s="2">
-        <v>20.0</v>
+        <v>20</v>
       </c>
       <c r="L22" s="2">
-        <v>22.0</v>
+        <v>22</v>
       </c>
       <c r="M22" s="2">
-        <v>24.0</v>
+        <v>24</v>
       </c>
       <c r="N22" s="2">
-        <v>26.0</v>
+        <v>26</v>
       </c>
       <c r="O22" s="2">
-        <v>28.0</v>
+        <v>28</v>
       </c>
       <c r="P22" s="2">
-        <v>30.0</v>
+        <v>30</v>
       </c>
       <c r="Q22" s="4">
         <f>AVERAGE(C22:P22)</f>
         <v>17</v>
       </c>
       <c r="R22" s="1">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="B23" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C23" s="1">
-        <v>3956.0</v>
+        <v>3956</v>
       </c>
       <c r="D23" s="1">
-        <v>2888.0</v>
+        <v>2888</v>
       </c>
       <c r="E23" s="1">
-        <v>2302.0</v>
+        <v>2302</v>
       </c>
       <c r="F23" s="1">
-        <v>1866.0</v>
+        <v>1866</v>
       </c>
       <c r="G23" s="1">
-        <v>1612.0</v>
+        <v>1612</v>
       </c>
       <c r="H23" s="1">
-        <v>1422.0</v>
+        <v>1422</v>
       </c>
       <c r="I23" s="1">
-        <v>1295.0</v>
+        <v>1295</v>
       </c>
       <c r="J23" s="1">
-        <v>1199.0</v>
+        <v>1199</v>
       </c>
       <c r="K23" s="1">
-        <v>1096.0</v>
+        <v>1096</v>
       </c>
       <c r="L23" s="1">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="M23" s="1">
-        <v>976.0</v>
+        <v>976</v>
       </c>
       <c r="N23" s="1">
-        <v>936.0</v>
+        <v>936</v>
       </c>
       <c r="O23" s="1">
-        <v>904.0</v>
+        <v>904</v>
       </c>
       <c r="P23" s="1">
-        <v>872.0</v>
-      </c>
-    </row>
-    <row r="24">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="C24" s="1">
-        <v>3955.0</v>
+        <v>3955</v>
       </c>
       <c r="D24" s="1">
-        <v>2896.0</v>
+        <v>2896</v>
       </c>
       <c r="E24" s="1">
-        <v>2302.0</v>
+        <v>2302</v>
       </c>
       <c r="F24" s="1">
-        <v>1865.0</v>
+        <v>1865</v>
       </c>
       <c r="G24" s="1">
-        <v>1612.0</v>
+        <v>1612</v>
       </c>
       <c r="H24" s="1">
-        <v>1421.0</v>
+        <v>1421</v>
       </c>
       <c r="I24" s="1">
-        <v>1295.0</v>
+        <v>1295</v>
       </c>
       <c r="J24" s="1">
-        <v>1199.0</v>
+        <v>1199</v>
       </c>
       <c r="K24" s="1">
-        <v>1096.0</v>
+        <v>1096</v>
       </c>
       <c r="L24" s="1">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="M24" s="1">
-        <v>972.0</v>
+        <v>972</v>
       </c>
       <c r="N24" s="1">
-        <v>936.0</v>
+        <v>936</v>
       </c>
       <c r="O24" s="1">
-        <v>904.0</v>
+        <v>904</v>
       </c>
       <c r="P24" s="1">
-        <v>872.0</v>
-      </c>
-    </row>
-    <row r="25">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="B25" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C25" s="1">
-        <v>3956.0</v>
+        <v>3956</v>
       </c>
       <c r="D25" s="1">
-        <v>2887.0</v>
+        <v>2887</v>
       </c>
       <c r="E25" s="1">
-        <v>2301.0</v>
+        <v>2301</v>
       </c>
       <c r="F25" s="1">
-        <v>1866.0</v>
+        <v>1866</v>
       </c>
       <c r="G25" s="1">
-        <v>1612.0</v>
+        <v>1612</v>
       </c>
       <c r="H25" s="1">
-        <v>1422.0</v>
+        <v>1422</v>
       </c>
       <c r="I25" s="1">
-        <v>1295.0</v>
+        <v>1295</v>
       </c>
       <c r="J25" s="1">
-        <v>1199.0</v>
+        <v>1199</v>
       </c>
       <c r="K25" s="1">
-        <v>1097.0</v>
+        <v>1097</v>
       </c>
       <c r="L25" s="1">
-        <v>1000.0</v>
+        <v>1000</v>
       </c>
       <c r="M25" s="1">
-        <v>974.0</v>
+        <v>974</v>
       </c>
       <c r="N25" s="1">
-        <v>935.0</v>
+        <v>935</v>
       </c>
       <c r="O25" s="1">
-        <v>904.0</v>
+        <v>904</v>
       </c>
       <c r="P25" s="1">
-        <v>872.0</v>
-      </c>
-    </row>
-    <row r="26">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="C26" s="3">
-        <f t="shared" ref="C26:P26" si="1">STDEV(C23:C25)</f>
-        <v>0.5773502692</v>
+        <f t="shared" ref="C26:P26" si="0">STDEV(C23:C25)</f>
+        <v>0.57735026918962584</v>
       </c>
       <c r="D26" s="3">
-        <f t="shared" si="1"/>
-        <v>4.932882862</v>
+        <f t="shared" si="0"/>
+        <v>4.932882862316248</v>
       </c>
       <c r="E26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="F26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="G26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="I26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="K26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962584</v>
       </c>
       <c r="L26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="M26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="N26" s="3">
-        <f t="shared" si="1"/>
-        <v>0.5773502692</v>
+        <f t="shared" si="0"/>
+        <v>0.57735026918962573</v>
       </c>
       <c r="O26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="P26" s="3">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="Q26" s="3">
         <f>AVERAGE(C26:P26)</f>
-        <v>0.7426417484</v>
+        <v>0.74264174838957175</v>
       </c>
       <c r="R26" s="1">
-        <v>6.0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>